--- a/Lora_and_SigFox_Devices/MeteoRain_IoT_Pro_Gen2/Customer_uplinks_downlinks_rain.xlsx
+++ b/Lora_and_SigFox_Devices/MeteoRain_IoT_Pro_Gen2/Customer_uplinks_downlinks_rain.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pavol\Documents\GitHub\FW_MeteoRain_IoT_Pro_Gen2\zDOC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pavol\Desktop\uplinks downlinks Gen2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EBA567-0135-4675-B23B-DAF2F6C0E419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA3AD4C-9E01-4486-9945-D7F04E021D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hárok1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
   <si>
     <t>UPLINKS</t>
   </si>
@@ -78,6 +78,12 @@
     <t>config OTAA</t>
   </si>
   <si>
+    <t>24b</t>
+  </si>
+  <si>
+    <t>24b - AppKey + AppEUI</t>
+  </si>
+  <si>
     <t>config ADR - Automatic Data Rate</t>
   </si>
   <si>
@@ -105,6 +111,9 @@
     <t>O1O2O3O4</t>
   </si>
   <si>
+    <t>O1-delay</t>
+  </si>
+  <si>
     <t>O2O3O4 - packets, minimum is O1O2, delay and 1 packet number</t>
   </si>
   <si>
@@ -138,19 +147,28 @@
     <t>4B</t>
   </si>
   <si>
+    <t>O1O2O3</t>
+  </si>
+  <si>
+    <t>Rejoin switch and counter</t>
+  </si>
+  <si>
     <t>O1 - does not  matter value of O1, reset will be after 60 seconds</t>
   </si>
   <si>
-    <t>0102030405060708090A0B0C0D0000000102030405060708</t>
-  </si>
-  <si>
-    <t>AppKey + AppEUI: AppKey = 0102030405060708090A0B0C0D000000 AppEUI = 0102030405060708</t>
-  </si>
-  <si>
-    <t>Example Data - in HEX</t>
-  </si>
-  <si>
-    <t>UNIX time</t>
+    <t>- see Excel</t>
+  </si>
+  <si>
+    <t>Set Data - in HEX</t>
+  </si>
+  <si>
+    <t>Timereq settings - timesync</t>
+  </si>
+  <si>
+    <t>O1 - ( 00 - OFF, 01 - ON ), O2O3 - 5…4095, messages after rejoin will be performed, minimum is 5, maximum is 4095</t>
+  </si>
+  <si>
+    <t>O1O2 - message count from 5 to 4095,how often we want timesync from network / messages count, default = 1000</t>
   </si>
 </sst>
 </file>
@@ -182,7 +200,7 @@
       <charset val="238"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -205,12 +223,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor rgb="FFFF9900"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -247,8 +259,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -510,14 +522,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:G23"/>
+  <dimension ref="A2:G27"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="38.140625" customWidth="1"/>
-    <col min="3" max="3" width="53.7109375" customWidth="1"/>
-    <col min="4" max="4" width="92.5703125" customWidth="1"/>
-    <col min="5" max="7" width="26.7109375" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" customWidth="1"/>
+    <col min="4" max="7" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="21" x14ac:dyDescent="0.35">
@@ -604,7 +615,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -619,21 +630,24 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>35</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>100</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -641,13 +655,13 @@
         <v>103</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -655,115 +669,146 @@
         <v>104</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
         <v>16</v>
       </c>
-      <c r="C15" t="s">
-        <v>14</v>
-      </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>107</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" t="s">
-        <v>19</v>
-      </c>
+      <c r="B16" s="10"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>20</v>
       </c>
       <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
         <v>21</v>
-      </c>
-      <c r="D17" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B18" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
         <v>23</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>24</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="11"/>
+      <c r="A20" s="1">
+        <v>110</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="6"/>
+        <v>36</v>
+      </c>
+      <c r="D21" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
+        <v>112</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="10"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>120</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="10"/>
+      <c r="E25" s="6"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>130</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+      <c r="B26" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>132</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" t="s">
-        <v>30</v>
+      <c r="B27" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
